--- a/public/docs/Plantillas Diplomas Cursos de Ley.xlsx
+++ b/public/docs/Plantillas Diplomas Cursos de Ley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{386304B1-E85C-464B-A794-00747DEE4653}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F9B552-0002-4EBC-9EF5-805830B0D3EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="263">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -673,10 +673,6 @@
   </si>
   <si>
     <t>Opcional
-Fecha Fin</t>
-  </si>
-  <si>
-    <t>Opcional
 Fecha Inicio</t>
   </si>
   <si>
@@ -703,9 +699,6 @@
     <t>docformato</t>
   </si>
   <si>
-    <t>fechafin</t>
-  </si>
-  <si>
     <t>fechainicio</t>
   </si>
   <si>
@@ -833,6 +826,9 @@
   </si>
   <si>
     <t>Capitán de Infantería de Marina</t>
+  </si>
+  <si>
+    <t>Validación</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2032,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>FECHA INICIO CURSO</a:t>
+            <a:t>FECHA INICIO Y FIN CURSO</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
@@ -2053,7 +2049,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 05 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 5 al 6 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -2068,111 +2064,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="CuadroTexto 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC111E91-FC70-2E1E-D591-1A369C47F238}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16436340" y="731520"/>
-          <a:ext cx="2026920" cy="434340"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>FECHA FIN CURSO</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2264,13 +2162,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2362,13 +2260,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2460,13 +2358,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -2542,13 +2440,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2624,13 +2522,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2706,13 +2604,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2978,13 +2876,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3061,7 +2959,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 06 de mayo de 2025)</a:t>
+            <a:t>(Ejemplo: 6 de mayo de 2025)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -3645,7 +3543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.8984375" style="24" customWidth="1"/>
@@ -3653,7 +3551,7 @@
     <col min="3" max="3" width="24" style="33" customWidth="1"/>
     <col min="4" max="4" width="34.59765625" style="24" customWidth="1"/>
     <col min="5" max="5" width="28.3984375" style="20" customWidth="1"/>
-    <col min="6" max="6" width="19.3984375" style="34" customWidth="1"/>
+    <col min="6" max="6" width="21.5" style="34" customWidth="1"/>
     <col min="7" max="7" width="21.59765625" style="23" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.3984375" style="25" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="25" hidden="1" customWidth="1"/>
@@ -3663,15 +3561,15 @@
     <col min="16" max="17" width="21.59765625" style="19" customWidth="1"/>
     <col min="18" max="18" width="29.3984375" style="19" customWidth="1"/>
     <col min="19" max="19" width="19.8984375" style="30" customWidth="1"/>
-    <col min="20" max="22" width="27.69921875" style="19" customWidth="1"/>
-    <col min="23" max="23" width="31.3984375" style="19" customWidth="1"/>
-    <col min="24" max="24" width="34" style="19" customWidth="1"/>
-    <col min="25" max="25" width="31.3984375" style="19" customWidth="1"/>
-    <col min="26" max="28" width="9.69921875" style="30" customWidth="1"/>
-    <col min="29" max="16384" width="10.5" style="3"/>
+    <col min="20" max="21" width="27.69921875" style="19" customWidth="1"/>
+    <col min="22" max="22" width="31.3984375" style="19" customWidth="1"/>
+    <col min="23" max="23" width="34" style="19" customWidth="1"/>
+    <col min="24" max="24" width="31.3984375" style="19" customWidth="1"/>
+    <col min="25" max="27" width="9.69921875" style="30" customWidth="1"/>
+    <col min="28" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3718,46 +3616,43 @@
         <v>213</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="Q1" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="S1" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="R1" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="S1" s="28" t="s">
-        <v>243</v>
-      </c>
       <c r="T1" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="W1" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="U1" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="W1" s="14" t="s">
-        <v>231</v>
-      </c>
       <c r="X1" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z1" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="Y1" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z1" s="35" t="s">
+      <c r="AA1" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="AA1" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="AB1" s="37" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:27" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -3768,7 +3663,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>6</v>
@@ -3801,49 +3696,46 @@
         <v>15</v>
       </c>
       <c r="O2" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="T2" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="S2" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="T2" s="15" t="s">
+      <c r="U2" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="X2" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="U2" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="V2" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="X2" s="15" t="s">
+      <c r="Y2" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="Z2" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="Y2" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z2" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AA2" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="AB2" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G3" s="19"/>
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
@@ -3853,27 +3745,27 @@
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
     </row>
-    <row r="4" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:28" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:27" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MpJBu3jMreu+MyGBwUxSHkfMJU7O4vHU7cOFaR1ao7T4zkvYY6fapZULpHNSD4GirINGPnspAaHeMjjZZS2wNw==" saltValue="7mrknlXMBRGp8fUkKagn9g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Upux1Li3z7f6MN3mC45VTS566Y+3hIlA9VohO+bE/eTZpcUzcJ8yl3kk3FhnZO0gm9IvMD9Yp6Na4njHRZ79Jg==" saltValue="uvCZVR3px+W1i1BgxfSW+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="T3:AB354 A3:R354" name="Rango1"/>
+    <protectedRange sqref="A3:R354 T3:AA354" name="Rango1"/>
     <protectedRange sqref="S3:S354" name="Rango1_1"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -3920,20 +3812,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C2:J196"/>
+  <dimension ref="A1:J196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.5" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="33.59765625" customWidth="1"/>
     <col min="5" max="6" width="10.5" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H2" s="38"/>
       <c r="I2" s="38"/>
     </row>
-    <row r="3" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
@@ -3941,13 +3839,13 @@
         <v>19</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="4:10" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>20</v>
       </c>
@@ -3955,13 +3853,13 @@
         <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="4:10" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>22</v>
       </c>
@@ -3969,104 +3867,104 @@
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="6" spans="4:10" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="4:10" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" spans="4:10" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="4:10" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" spans="4:10" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="4:10" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>28</v>
       </c>
       <c r="J11" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="12" spans="4:10" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="4:10" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>30</v>
       </c>
       <c r="J13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="14" spans="4:10" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="15" spans="4:10" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16" spans="4:10" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>33</v>
       </c>
       <c r="J16" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.3">
@@ -4074,7 +3972,7 @@
         <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.3">
@@ -4154,7 +4052,7 @@
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
@@ -4187,7 +4085,7 @@
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s">
         <v>55</v>
@@ -4200,7 +4098,7 @@
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D41" t="s">
         <v>57</v>
